--- a/dtm_dashboard/excel_data/keeping_prr/Нижнекамск/Апрель 2026.xlsx
+++ b/dtm_dashboard/excel_data/keeping_prr/Нижнекамск/Апрель 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 16.04.2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 30.04.2026</t>
   </si>
   <si>
     <t>Отбор:</t>
@@ -98,6 +98,48 @@
   </si>
   <si>
     <t>16.04.2026</t>
+  </si>
+  <si>
+    <t>17.04.2026</t>
+  </si>
+  <si>
+    <t>18.04.2026</t>
+  </si>
+  <si>
+    <t>19.04.2026</t>
+  </si>
+  <si>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>21.04.2026</t>
+  </si>
+  <si>
+    <t>22.04.2026</t>
+  </si>
+  <si>
+    <t>23.04.2026</t>
+  </si>
+  <si>
+    <t>24.04.2026</t>
+  </si>
+  <si>
+    <t>25.04.2026</t>
+  </si>
+  <si>
+    <t>26.04.2026</t>
+  </si>
+  <si>
+    <t>27.04.2026</t>
+  </si>
+  <si>
+    <t>28.04.2026</t>
+  </si>
+  <si>
+    <t>29.04.2026</t>
+  </si>
+  <si>
+    <t>30.04.2026</t>
   </si>
   <si>
     <t>Итого</t>
@@ -349,7 +391,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="J23"/>
+  <dimension ref="J37"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="8.66796875" style="1" customWidth="true"/>
@@ -700,28 +742,224 @@
       <c r="I22" s="12" t="e"/>
       <c r="J22" s="13" t="e"/>
     </row>
-    <row r="23" ht="13" customHeight="true">
-      <c r="A23" s="17" t="s">
+    <row r="23" ht="11" customHeight="true">
+      <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="17" t="e"/>
-      <c r="C23" s="17" t="e"/>
-      <c r="D23" s="18" t="e"/>
-      <c r="E23" s="19" t="n">
+      <c r="B23" s="5" t="e"/>
+      <c r="C23" s="5" t="e"/>
+      <c r="D23" s="6" t="e"/>
+      <c r="E23" s="6" t="e"/>
+      <c r="F23" s="12" t="e"/>
+      <c r="G23" s="13" t="e"/>
+      <c r="H23" s="6" t="e"/>
+      <c r="I23" s="8" t="e"/>
+      <c r="J23" s="9" t="e"/>
+    </row>
+    <row r="24" ht="11" customHeight="true">
+      <c r="A24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="5" t="e"/>
+      <c r="C24" s="5" t="e"/>
+      <c r="D24" s="6" t="e"/>
+      <c r="E24" s="6" t="e"/>
+      <c r="F24" s="12" t="e"/>
+      <c r="G24" s="13" t="e"/>
+      <c r="H24" s="6" t="e"/>
+      <c r="I24" s="8" t="e"/>
+      <c r="J24" s="9" t="e"/>
+    </row>
+    <row r="25" ht="11" customHeight="true">
+      <c r="A25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="5" t="e"/>
+      <c r="C25" s="5" t="e"/>
+      <c r="D25" s="6" t="e"/>
+      <c r="E25" s="6" t="e"/>
+      <c r="F25" s="12" t="e"/>
+      <c r="G25" s="13" t="e"/>
+      <c r="H25" s="6" t="e"/>
+      <c r="I25" s="8" t="e"/>
+      <c r="J25" s="9" t="e"/>
+    </row>
+    <row r="26" ht="11" customHeight="true">
+      <c r="A26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="5" t="e"/>
+      <c r="C26" s="5" t="e"/>
+      <c r="D26" s="6" t="e"/>
+      <c r="E26" s="6" t="e"/>
+      <c r="F26" s="12" t="e"/>
+      <c r="G26" s="13" t="e"/>
+      <c r="H26" s="6" t="e"/>
+      <c r="I26" s="8" t="e"/>
+      <c r="J26" s="9" t="e"/>
+    </row>
+    <row r="27" ht="11" customHeight="true">
+      <c r="A27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="5" t="e"/>
+      <c r="C27" s="5" t="e"/>
+      <c r="D27" s="6" t="e"/>
+      <c r="E27" s="6" t="e"/>
+      <c r="F27" s="12" t="e"/>
+      <c r="G27" s="13" t="e"/>
+      <c r="H27" s="6" t="e"/>
+      <c r="I27" s="8" t="e"/>
+      <c r="J27" s="9" t="e"/>
+    </row>
+    <row r="28" ht="11" customHeight="true">
+      <c r="A28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5" t="e"/>
+      <c r="C28" s="5" t="e"/>
+      <c r="D28" s="6" t="e"/>
+      <c r="E28" s="6" t="e"/>
+      <c r="F28" s="12" t="e"/>
+      <c r="G28" s="13" t="e"/>
+      <c r="H28" s="6" t="e"/>
+      <c r="I28" s="8" t="e"/>
+      <c r="J28" s="9" t="e"/>
+    </row>
+    <row r="29" ht="11" customHeight="true">
+      <c r="A29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="5" t="e"/>
+      <c r="C29" s="5" t="e"/>
+      <c r="D29" s="6" t="e"/>
+      <c r="E29" s="6" t="e"/>
+      <c r="F29" s="12" t="e"/>
+      <c r="G29" s="13" t="e"/>
+      <c r="H29" s="6" t="e"/>
+      <c r="I29" s="8" t="e"/>
+      <c r="J29" s="9" t="e"/>
+    </row>
+    <row r="30" ht="11" customHeight="true">
+      <c r="A30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="5" t="e"/>
+      <c r="C30" s="5" t="e"/>
+      <c r="D30" s="6" t="e"/>
+      <c r="E30" s="6" t="e"/>
+      <c r="F30" s="12" t="e"/>
+      <c r="G30" s="13" t="e"/>
+      <c r="H30" s="6" t="e"/>
+      <c r="I30" s="8" t="e"/>
+      <c r="J30" s="9" t="e"/>
+    </row>
+    <row r="31" ht="11" customHeight="true">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="5" t="e"/>
+      <c r="C31" s="5" t="e"/>
+      <c r="D31" s="6" t="e"/>
+      <c r="E31" s="6" t="e"/>
+      <c r="F31" s="12" t="e"/>
+      <c r="G31" s="13" t="e"/>
+      <c r="H31" s="6" t="e"/>
+      <c r="I31" s="8" t="e"/>
+      <c r="J31" s="9" t="e"/>
+    </row>
+    <row r="32" ht="11" customHeight="true">
+      <c r="A32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="5" t="e"/>
+      <c r="C32" s="5" t="e"/>
+      <c r="D32" s="6" t="e"/>
+      <c r="E32" s="6" t="e"/>
+      <c r="F32" s="12" t="e"/>
+      <c r="G32" s="13" t="e"/>
+      <c r="H32" s="6" t="e"/>
+      <c r="I32" s="8" t="e"/>
+      <c r="J32" s="9" t="e"/>
+    </row>
+    <row r="33" ht="11" customHeight="true">
+      <c r="A33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="5" t="e"/>
+      <c r="C33" s="5" t="e"/>
+      <c r="D33" s="6" t="e"/>
+      <c r="E33" s="6" t="e"/>
+      <c r="F33" s="12" t="e"/>
+      <c r="G33" s="13" t="e"/>
+      <c r="H33" s="6" t="e"/>
+      <c r="I33" s="8" t="e"/>
+      <c r="J33" s="9" t="e"/>
+    </row>
+    <row r="34" ht="11" customHeight="true">
+      <c r="A34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="5" t="e"/>
+      <c r="C34" s="5" t="e"/>
+      <c r="D34" s="6" t="e"/>
+      <c r="E34" s="6" t="e"/>
+      <c r="F34" s="12" t="e"/>
+      <c r="G34" s="13" t="e"/>
+      <c r="H34" s="6" t="e"/>
+      <c r="I34" s="8" t="e"/>
+      <c r="J34" s="9" t="e"/>
+    </row>
+    <row r="35" ht="11" customHeight="true">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="e"/>
+      <c r="C35" s="5" t="e"/>
+      <c r="D35" s="6" t="e"/>
+      <c r="E35" s="6" t="e"/>
+      <c r="F35" s="12" t="e"/>
+      <c r="G35" s="13" t="e"/>
+      <c r="H35" s="6" t="e"/>
+      <c r="I35" s="8" t="e"/>
+      <c r="J35" s="9" t="e"/>
+    </row>
+    <row r="36" ht="11" customHeight="true">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="e"/>
+      <c r="C36" s="5" t="e"/>
+      <c r="D36" s="6" t="e"/>
+      <c r="E36" s="6" t="e"/>
+      <c r="F36" s="12" t="e"/>
+      <c r="G36" s="13" t="e"/>
+      <c r="H36" s="6" t="e"/>
+      <c r="I36" s="8" t="e"/>
+      <c r="J36" s="9" t="e"/>
+    </row>
+    <row r="37" ht="13" customHeight="true">
+      <c r="A37" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="17" t="e"/>
+      <c r="C37" s="17" t="e"/>
+      <c r="D37" s="18" t="e"/>
+      <c r="E37" s="19" t="n">
         <v>1308.329</v>
       </c>
-      <c r="F23" s="20" t="e"/>
-      <c r="G23" s="21" t="e"/>
-      <c r="H23" s="22" t="n">
+      <c r="F37" s="20" t="e"/>
+      <c r="G37" s="21" t="e"/>
+      <c r="H37" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I37" s="23" t="n">
         <v>2.536</v>
       </c>
-      <c r="J23" s="23" t="e"/>
+      <c r="J37" s="23" t="e"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="52">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="I6:J6"/>
@@ -759,7 +997,21 @@
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="I37:J37"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>
